--- a/public/sap-reporting/expansion-150-downloads/EXT-FI25-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI25-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R87ea170880b24d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R20c1544dfc124567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rc409adbae8b0427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R236a430f298947be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R8f10a488c2c2400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R6aabc4b028844e0a"/>
   </x:sheets>
 </x:workbook>
 </file>
